--- a/sheets/조재수대금교본/검수/이등병의 편지.xlsx
+++ b/sheets/조재수대금교본/검수/이등병의 편지.xlsx
@@ -3457,7 +3457,7 @@
       <c r="I4" s="23"/>
       <c r="J4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">ㄴ潢潢ㄴ
+          <t xml:space="preserve">潢潢
 –</t>
         </is>
       </c>
@@ -3481,11 +3481,7 @@
       <c r="A5" s="0"/>
       <c r="B5" s="21"/>
       <c r="C5" s="23"/>
-      <c r="D5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D5" s="21"/>
       <c r="E5" s="23"/>
       <c r="F5" s="21"/>
       <c r="G5" s="23"/>
@@ -3655,29 +3651,13 @@
       <c r="A10" s="0"/>
       <c r="B10" s="21"/>
       <c r="C10" s="24"/>
-      <c r="D10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D10" s="21"/>
       <c r="E10" s="24"/>
-      <c r="F10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F10" s="21"/>
       <c r="G10" s="24"/>
-      <c r="H10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H10" s="21"/>
       <c r="I10" s="24"/>
-      <c r="J10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J10" s="21"/>
       <c r="K10" s="24"/>
       <c r="L10" s="21"/>
       <c r="M10" s="24"/>
@@ -3712,7 +3692,7 @@
       <c r="J11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-潢ㄴ</t>
+潢</t>
         </is>
       </c>
       <c r="K11" s="22"/>
@@ -3822,16 +3802,11 @@
         </is>
       </c>
       <c r="C14" s="24"/>
-      <c r="D14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ㅂ</t>
-        </is>
-      </c>
+      <c r="D14" s="21"/>
       <c r="E14" s="24"/>
       <c r="F14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌
-‹</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="G14" s="24"/>
@@ -3866,11 +3841,7 @@
       <c r="A15" s="0"/>
       <c r="B15" s="21"/>
       <c r="C15" s="22"/>
-      <c r="D15" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D15" s="21"/>
       <c r="E15" s="22"/>
       <c r="F15" s="21" t="inlineStr">
         <is>
@@ -3896,7 +3867,7 @@
       <c r="L15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">太
-黃ㄴ</t>
+黃</t>
         </is>
       </c>
       <c r="M15" s="22"/>
@@ -3915,12 +3886,7 @@
         </is>
       </c>
       <c r="C16" s="23"/>
-      <c r="D16" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ㅂ
-‹</t>
-        </is>
-      </c>
+      <c r="D16" s="21"/>
       <c r="E16" s="23"/>
       <c r="F16" s="21" t="inlineStr">
         <is>
@@ -3957,11 +3923,7 @@
         </is>
       </c>
       <c r="C17" s="23"/>
-      <c r="D17" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ㅂ</t>
-        </is>
-      </c>
+      <c r="D17" s="21"/>
       <c r="E17" s="23"/>
       <c r="F17" s="21"/>
       <c r="G17" s="23"/>
@@ -3992,17 +3954,9 @@
         </is>
       </c>
       <c r="G18" s="24"/>
-      <c r="H18" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H18" s="21"/>
       <c r="I18" s="24"/>
-      <c r="J18" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J18" s="21"/>
       <c r="K18" s="24"/>
       <c r="L18" s="21"/>
       <c r="M18" s="24"/>

--- a/sheets/조재수대금교본/검수/이등병의 편지.xlsx
+++ b/sheets/조재수대금교본/검수/이등병의 편지.xlsx
@@ -3457,7 +3457,7 @@
       <c r="I4" s="23"/>
       <c r="J4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢潢
+          <t xml:space="preserve">ㄴ潢潢ㄴ
 –</t>
         </is>
       </c>
@@ -3692,7 +3692,7 @@
       <c r="J11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-潢</t>
+潢ㄴ</t>
         </is>
       </c>
       <c r="K11" s="22"/>
@@ -3802,7 +3802,11 @@
         </is>
       </c>
       <c r="C14" s="24"/>
-      <c r="D14" s="21"/>
+      <c r="D14" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ㅂ</t>
+        </is>
+      </c>
       <c r="E14" s="24"/>
       <c r="F14" s="21" t="inlineStr">
         <is>
@@ -3867,7 +3871,7 @@
       <c r="L15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">太
-黃</t>
+黃ㄴ</t>
         </is>
       </c>
       <c r="M15" s="22"/>
@@ -3886,7 +3890,11 @@
         </is>
       </c>
       <c r="C16" s="23"/>
-      <c r="D16" s="21"/>
+      <c r="D16" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ㅂ</t>
+        </is>
+      </c>
       <c r="E16" s="23"/>
       <c r="F16" s="21" t="inlineStr">
         <is>
@@ -3923,7 +3931,11 @@
         </is>
       </c>
       <c r="C17" s="23"/>
-      <c r="D17" s="21"/>
+      <c r="D17" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ㅂ</t>
+        </is>
+      </c>
       <c r="E17" s="23"/>
       <c r="F17" s="21"/>
       <c r="G17" s="23"/>

--- a/sheets/조재수대금교본/검수/이등병의 편지.xlsx
+++ b/sheets/조재수대금교본/검수/이등병의 편지.xlsx
@@ -3343,26 +3343,26 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="19.86" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="19.86" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="19.86" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="19.86" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="19.86" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="19.86" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="19.86" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="81.63" customHeight="true">
+    <row r="2" ht="86.96" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
       <c r="N2" s="20"/>
       <c r="O2" s="20"/>
     </row>
-    <row r="3" ht="91.25" customHeight="true">
+    <row r="3" ht="97.23" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
       </c>
       <c r="O3" s="22"/>
     </row>
-    <row r="4" ht="91.25" customHeight="true">
+    <row r="4" ht="97.23" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -3477,7 +3477,7 @@
       </c>
       <c r="O4" s="23"/>
     </row>
-    <row r="5" ht="91.25" customHeight="true">
+    <row r="5" ht="97.23" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21"/>
       <c r="C5" s="23"/>
@@ -3494,7 +3494,7 @@
       <c r="N5" s="21"/>
       <c r="O5" s="23"/>
     </row>
-    <row r="6" ht="91.25" customHeight="true">
+    <row r="6" ht="97.23" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -3537,7 +3537,7 @@
       </c>
       <c r="O6" s="24"/>
     </row>
-    <row r="7" ht="91.25" customHeight="true">
+    <row r="7" ht="97.23" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -3583,7 +3583,7 @@
       </c>
       <c r="O7" s="22"/>
     </row>
-    <row r="8" ht="91.25" customHeight="true">
+    <row r="8" ht="97.23" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -3630,7 +3630,7 @@
       </c>
       <c r="O8" s="23"/>
     </row>
-    <row r="9" ht="91.25" customHeight="true">
+    <row r="9" ht="97.23" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21"/>
       <c r="C9" s="23"/>
@@ -3647,7 +3647,7 @@
       <c r="N9" s="21"/>
       <c r="O9" s="23"/>
     </row>
-    <row r="10" ht="91.25" customHeight="true">
+    <row r="10" ht="97.23" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21"/>
       <c r="C10" s="24"/>
@@ -3664,7 +3664,7 @@
       <c r="N10" s="21"/>
       <c r="O10" s="24"/>
     </row>
-    <row r="11" ht="91.25" customHeight="true">
+    <row r="11" ht="97.23" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="O11" s="22"/>
     </row>
-    <row r="12" ht="91.25" customHeight="true">
+    <row r="12" ht="97.23" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -3752,7 +3752,7 @@
       </c>
       <c r="O12" s="23"/>
     </row>
-    <row r="13" ht="91.25" customHeight="true">
+    <row r="13" ht="97.23" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -3794,7 +3794,7 @@
       </c>
       <c r="O13" s="23"/>
     </row>
-    <row r="14" ht="91.25" customHeight="true">
+    <row r="14" ht="97.23" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -3841,7 +3841,7 @@
       </c>
       <c r="O14" s="24"/>
     </row>
-    <row r="15" ht="91.25" customHeight="true">
+    <row r="15" ht="97.23" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21"/>
       <c r="C15" s="22"/>
@@ -3882,7 +3882,7 @@
       </c>
       <c r="O15" s="22"/>
     </row>
-    <row r="16" ht="91.25" customHeight="true">
+    <row r="16" ht="97.23" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
       <c r="N16" s="21"/>
       <c r="O16" s="23"/>
     </row>
-    <row r="17" ht="91.25" customHeight="true">
+    <row r="17" ht="97.23" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21" t="inlineStr">
         <is>
@@ -3948,7 +3948,7 @@
       <c r="N17" s="21"/>
       <c r="O17" s="23"/>
     </row>
-    <row r="18" ht="91.25" customHeight="true">
+    <row r="18" ht="97.23" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21" t="inlineStr">
         <is>
@@ -3985,6 +3985,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="49"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="46"/>
 </worksheet>
 </file>